--- a/research/traditional_assets/database/data/egypt/egypt_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/egypt/egypt_financial_svcs_non_bank_insurance.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ8"/>
+  <dimension ref="A1:AQ9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,13 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0621</v>
+        <v>-0.05010000000000001</v>
       </c>
       <c r="E2">
-        <v>0.136</v>
-      </c>
-      <c r="F2">
-        <v>0.15</v>
+        <v>0.06958</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -609,28 +606,28 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>122.47</v>
+        <v>120.18</v>
       </c>
       <c r="L2">
-        <v>0.2552787910369984</v>
+        <v>0.2957185039370079</v>
       </c>
       <c r="M2">
-        <v>42.89</v>
+        <v>52.87</v>
       </c>
       <c r="N2">
-        <v>0.04570545609548167</v>
+        <v>0.06285068949120304</v>
       </c>
       <c r="O2">
-        <v>0.3502082142565526</v>
+        <v>0.4399234481610916</v>
       </c>
       <c r="P2">
-        <v>42.89</v>
+        <v>52.87</v>
       </c>
       <c r="Q2">
-        <v>0.04570545609548167</v>
+        <v>0.06285068949120304</v>
       </c>
       <c r="R2">
-        <v>0.3502082142565526</v>
+        <v>0.4399234481610916</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -639,61 +636,61 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>171.74</v>
+        <v>433.67</v>
       </c>
       <c r="V2">
-        <v>0.1830136402387042</v>
+        <v>0.5155373276271993</v>
       </c>
       <c r="W2">
-        <v>0.1671131527797112</v>
+        <v>0.1047305843663041</v>
       </c>
       <c r="X2">
-        <v>0.05440697992409672</v>
+        <v>0.08920636363396592</v>
       </c>
       <c r="Y2">
-        <v>0.1127061728556144</v>
+        <v>0.01552422073233815</v>
       </c>
       <c r="Z2">
-        <v>0.2357412767128403</v>
+        <v>0.1892891410259993</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.0533302376592321</v>
+        <v>0.08897998181366135</v>
       </c>
       <c r="AC2">
-        <v>-0.0533302376592321</v>
+        <v>-0.08897998181366135</v>
       </c>
       <c r="AD2">
-        <v>1282.8</v>
+        <v>1439.818</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>1282.8</v>
+        <v>1439.818</v>
       </c>
       <c r="AG2">
-        <v>1111.06</v>
+        <v>1006.148</v>
       </c>
       <c r="AH2">
-        <v>0.5775256618044301</v>
+        <v>0.6312172898241049</v>
       </c>
       <c r="AI2">
-        <v>0.5338327091136079</v>
+        <v>0.5526669937026384</v>
       </c>
       <c r="AJ2">
-        <v>0.5421232910132425</v>
+        <v>0.5446445390906315</v>
       </c>
       <c r="AK2">
-        <v>0.497951829907765</v>
+        <v>0.4633321483107903</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-0.757</v>
+        <v>-0.571</v>
       </c>
       <c r="AQ2">
         <v>-0</v>
@@ -707,7 +704,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Naeem Holding Company For Investments (S.A.E - Free Zone) (CASE:NAHO)</t>
+          <t>Orascom Financial Holding S.A.E. (CASE:OFH)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -715,26 +712,8 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D3">
-        <v>0.09039999999999999</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
       <c r="K3">
-        <v>-2.21</v>
-      </c>
-      <c r="L3">
-        <v>-0.1323353293413174</v>
+        <v>0</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -742,71 +721,65 @@
       <c r="N3">
         <v>-0</v>
       </c>
-      <c r="O3">
-        <v>0</v>
-      </c>
       <c r="P3">
         <v>-0</v>
       </c>
       <c r="Q3">
         <v>-0</v>
       </c>
-      <c r="R3">
-        <v>0</v>
-      </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>6.72</v>
+        <v>37.4</v>
       </c>
       <c r="V3">
-        <v>0.08637532133676093</v>
+        <v>0.700374531835206</v>
       </c>
       <c r="W3">
-        <v>-0.01067117334620956</v>
+        <v>0</v>
       </c>
       <c r="X3">
-        <v>0.03784370469048893</v>
+        <v>0.06316116379580984</v>
       </c>
       <c r="Y3">
-        <v>-0.04851487803669849</v>
+        <v>-0.06316116379580984</v>
       </c>
       <c r="Z3">
-        <v>0.09849601887348863</v>
+        <v>0</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.04161736241639404</v>
+        <v>0.06323738105860478</v>
       </c>
       <c r="AC3">
-        <v>-0.04161736241639404</v>
+        <v>-0.06323738105860478</v>
       </c>
       <c r="AD3">
-        <v>23</v>
+        <v>0.118</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>23</v>
+        <v>0.118</v>
       </c>
       <c r="AG3">
-        <v>16.28</v>
+        <v>-37.282</v>
       </c>
       <c r="AH3">
-        <v>0.2281746031746032</v>
+        <v>0.002204865652677604</v>
       </c>
       <c r="AI3">
-        <v>0.08812260536398467</v>
+        <v>0.0008931409800330008</v>
       </c>
       <c r="AJ3">
-        <v>0.1730442176870748</v>
+        <v>-2.31306613723787</v>
       </c>
       <c r="AK3">
-        <v>0.06402391064967752</v>
+        <v>-0.3936105069786102</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -823,7 +796,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Contact Financial Holding S.A.E. (CASE:SRWA)</t>
+          <t>Naeem Holding Company For Investments (S.A.E - Free Zone) (CASE:NAHO)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -831,6 +804,12 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D4">
+        <v>-0.134</v>
+      </c>
+      <c r="E4">
+        <v>-0.0924</v>
+      </c>
       <c r="G4">
         <v>0</v>
       </c>
@@ -844,85 +823,82 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>31.1</v>
+        <v>2.83</v>
       </c>
       <c r="L4">
-        <v>0.3088381330685204</v>
+        <v>0.3130530973451328</v>
       </c>
       <c r="M4">
-        <v>13.2</v>
+        <v>-0</v>
       </c>
       <c r="N4">
-        <v>0.04225352112676056</v>
+        <v>-0</v>
       </c>
       <c r="O4">
-        <v>0.4244372990353698</v>
+        <v>-0</v>
       </c>
       <c r="P4">
-        <v>13.2</v>
+        <v>-0</v>
       </c>
       <c r="Q4">
-        <v>0.04225352112676056</v>
+        <v>-0</v>
       </c>
       <c r="R4">
-        <v>0.4244372990353698</v>
+        <v>-0</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
       <c r="U4">
-        <v>6.97</v>
+        <v>4.31</v>
       </c>
       <c r="V4">
-        <v>0.02231113956466069</v>
+        <v>0.08086303939962476</v>
       </c>
       <c r="W4">
-        <v>0.2446892210857593</v>
+        <v>0.01382510991695164</v>
       </c>
       <c r="X4">
-        <v>0.0406322153967963</v>
+        <v>0.06835300221560923</v>
       </c>
       <c r="Y4">
-        <v>0.204057005688963</v>
+        <v>-0.05452789229865759</v>
       </c>
       <c r="Z4">
-        <v>0.4488122297989928</v>
+        <v>0.05443159922928709</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.04515448828072251</v>
+        <v>0.07280026525643954</v>
       </c>
       <c r="AC4">
-        <v>-0.04515448828072251</v>
+        <v>-0.07280026525643954</v>
       </c>
       <c r="AD4">
-        <v>153.1</v>
+        <v>14.8</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>153.1</v>
+        <v>14.8</v>
       </c>
       <c r="AG4">
-        <v>146.13</v>
+        <v>10.49</v>
       </c>
       <c r="AH4">
-        <v>0.3288936627282492</v>
+        <v>0.2173274596182085</v>
       </c>
       <c r="AI4">
-        <v>0.4927582877373672</v>
+        <v>0.05875347360063517</v>
       </c>
       <c r="AJ4">
-        <v>0.3186923429219462</v>
+        <v>0.1644458379056279</v>
       </c>
       <c r="AK4">
-        <v>0.4811180983109998</v>
+        <v>0.04236843168140879</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -953,9 +929,6 @@
       <c r="E5">
         <v>0.136</v>
       </c>
-      <c r="F5">
-        <v>0.11</v>
-      </c>
       <c r="G5">
         <v>0</v>
       </c>
@@ -996,55 +969,55 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>66.40000000000001</v>
+        <v>291.6</v>
       </c>
       <c r="V5">
-        <v>0.3505807814149947</v>
+        <v>1.146677152968934</v>
       </c>
       <c r="W5">
-        <v>0.1098726114649681</v>
+        <v>0.1047305843663041</v>
       </c>
       <c r="X5">
-        <v>0.0412893937673218</v>
+        <v>0.07014568458973197</v>
       </c>
       <c r="Y5">
-        <v>0.06858321769764635</v>
+        <v>0.0345848997765721</v>
       </c>
       <c r="Z5">
-        <v>0.3427723224480475</v>
+        <v>0.3794236602628918</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.04585768793316604</v>
+        <v>0.0752158246877923</v>
       </c>
       <c r="AC5">
-        <v>-0.04585768793316604</v>
+        <v>-0.0752158246877923</v>
       </c>
       <c r="AD5">
-        <v>101.5</v>
+        <v>94.8</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>101.5</v>
+        <v>94.8</v>
       </c>
       <c r="AG5">
-        <v>35.09999999999999</v>
+        <v>-196.8</v>
       </c>
       <c r="AH5">
-        <v>0.3489171536610519</v>
+        <v>0.2715554282440561</v>
       </c>
       <c r="AI5">
-        <v>0.1921984472637758</v>
+        <v>0.2</v>
       </c>
       <c r="AJ5">
-        <v>0.156347438752784</v>
+        <v>-3.422608695652174</v>
       </c>
       <c r="AK5">
-        <v>0.07602339181286548</v>
+        <v>-1.078947368421053</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1061,7 +1034,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CI Capital Holding For Financial Investments (S.A.E) (CASE:CICH)</t>
+          <t>Contact Financial Holding S.A.E. (CASE:CNFN)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1069,9 +1042,6 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="F6">
-        <v>0.15</v>
-      </c>
       <c r="G6">
         <v>0</v>
       </c>
@@ -1085,28 +1055,28 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>38.1</v>
+        <v>24.1</v>
       </c>
       <c r="L6">
-        <v>0.2254437869822485</v>
+        <v>0.2104803493449782</v>
       </c>
       <c r="M6">
-        <v>24.2</v>
+        <v>17.8</v>
       </c>
       <c r="N6">
-        <v>0.08966283808818082</v>
+        <v>0.09314495028780743</v>
       </c>
       <c r="O6">
-        <v>0.6351706036745406</v>
+        <v>0.7385892116182573</v>
       </c>
       <c r="P6">
-        <v>24.2</v>
+        <v>17.8</v>
       </c>
       <c r="Q6">
-        <v>0.08966283808818082</v>
+        <v>0.09314495028780743</v>
       </c>
       <c r="R6">
-        <v>0.6351706036745406</v>
+        <v>0.7385892116182573</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1115,55 +1085,55 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>73.8</v>
+        <v>26.8</v>
       </c>
       <c r="V6">
-        <v>0.2734346054094109</v>
+        <v>0.1402407116692831</v>
       </c>
       <c r="W6">
-        <v>0.2033084311632871</v>
+        <v>0.1579292267365662</v>
       </c>
       <c r="X6">
-        <v>0.06752456608087165</v>
+        <v>0.08920636363396592</v>
       </c>
       <c r="Y6">
-        <v>0.1357838650824154</v>
+        <v>0.06872286310260028</v>
       </c>
       <c r="Z6">
-        <v>0.2300258608956037</v>
+        <v>0.3853661820140011</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.06080278738529817</v>
+        <v>0.08897998181366135</v>
       </c>
       <c r="AC6">
-        <v>-0.06080278738529817</v>
+        <v>-0.08897998181366135</v>
       </c>
       <c r="AD6">
-        <v>638.4</v>
+        <v>264.5</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>638.4</v>
+        <v>264.5</v>
       </c>
       <c r="AG6">
-        <v>564.6</v>
+        <v>237.7</v>
       </c>
       <c r="AH6">
-        <v>0.7028514807882859</v>
+        <v>0.5805531167690957</v>
       </c>
       <c r="AI6">
-        <v>0.7401739130434782</v>
+        <v>0.6444931773879142</v>
       </c>
       <c r="AJ6">
-        <v>0.6765727980826842</v>
+        <v>0.5543376865671642</v>
       </c>
       <c r="AK6">
-        <v>0.7158615443134272</v>
+        <v>0.6196558915537017</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1180,7 +1150,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>International Company for Leasing S.A.E. (CASE:ICLE)</t>
+          <t>CI Capital Holding For Financial Investments (S.A.E) (CASE:CICH)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1188,12 +1158,6 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D7">
-        <v>-0.241</v>
-      </c>
-      <c r="E7">
-        <v>0.00716</v>
-      </c>
       <c r="G7">
         <v>0</v>
       </c>
@@ -1207,28 +1171,28 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>5.42</v>
+        <v>38.6</v>
       </c>
       <c r="L7">
-        <v>0.5616580310880829</v>
+        <v>0.4200217627856366</v>
       </c>
       <c r="M7">
-        <v>4.06</v>
+        <v>29</v>
       </c>
       <c r="N7">
-        <v>0.07777777777777777</v>
+        <v>0.1230899830220713</v>
       </c>
       <c r="O7">
-        <v>0.7490774907749077</v>
+        <v>0.7512953367875648</v>
       </c>
       <c r="P7">
-        <v>4.06</v>
+        <v>29</v>
       </c>
       <c r="Q7">
-        <v>0.07777777777777777</v>
+        <v>0.1230899830220713</v>
       </c>
       <c r="R7">
-        <v>0.7490774907749077</v>
+        <v>0.7512953367875648</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1237,64 +1201,61 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>6.45</v>
+        <v>60.2</v>
       </c>
       <c r="V7">
-        <v>0.1235632183908046</v>
+        <v>0.2555178268251274</v>
       </c>
       <c r="W7">
-        <v>0.1309178743961353</v>
+        <v>0.185309649543927</v>
       </c>
       <c r="X7">
-        <v>0.0779450165977911</v>
+        <v>0.1240943006981008</v>
       </c>
       <c r="Y7">
-        <v>0.05297285779834418</v>
+        <v>0.0612153488458262</v>
       </c>
       <c r="Z7">
-        <v>0.04035799422859772</v>
+        <v>0.1224190755295058</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.06462889389349548</v>
+        <v>0.1017046728872097</v>
       </c>
       <c r="AC7">
-        <v>-0.06462889389349548</v>
+        <v>-0.1017046728872097</v>
       </c>
       <c r="AD7">
-        <v>161.4</v>
+        <v>762.2</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>161.4</v>
+        <v>762.2</v>
       </c>
       <c r="AG7">
-        <v>154.95</v>
+        <v>702</v>
       </c>
       <c r="AH7">
-        <v>0.7556179775280898</v>
+        <v>0.7638805371817999</v>
       </c>
       <c r="AI7">
-        <v>0.7861665854846566</v>
+        <v>0.7844792095512557</v>
       </c>
       <c r="AJ7">
-        <v>0.7480086893555394</v>
+        <v>0.7487201365187713</v>
       </c>
       <c r="AK7">
-        <v>0.7792305758109127</v>
+        <v>0.7702435813034891</v>
       </c>
       <c r="AL7">
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>-0.34</v>
-      </c>
-      <c r="AQ7">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1305,123 +1266,245 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>International Company for Leasing S.A.E. (CASE:ICLE)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D8">
+        <v>-0.255</v>
+      </c>
+      <c r="E8">
+        <v>0.00316</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>4.59</v>
+      </c>
+      <c r="L8">
+        <v>0.6322314049586777</v>
+      </c>
+      <c r="M8">
+        <v>4.64</v>
+      </c>
+      <c r="N8">
+        <v>0.1397590361445783</v>
+      </c>
+      <c r="O8">
+        <v>1.010893246187364</v>
+      </c>
+      <c r="P8">
+        <v>4.64</v>
+      </c>
+      <c r="Q8">
+        <v>0.1397590361445783</v>
+      </c>
+      <c r="R8">
+        <v>1.010893246187364</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>3.52</v>
+      </c>
+      <c r="V8">
+        <v>0.1060240963855422</v>
+      </c>
+      <c r="W8">
+        <v>0.1045558086560364</v>
+      </c>
+      <c r="X8">
+        <v>0.153610821079894</v>
+      </c>
+      <c r="Y8">
+        <v>-0.0490550124238576</v>
+      </c>
+      <c r="Z8">
+        <v>0.03650993210963037</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0.1073617312023741</v>
+      </c>
+      <c r="AC8">
+        <v>-0.1073617312023741</v>
+      </c>
+      <c r="AD8">
+        <v>159.4</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>159.4</v>
+      </c>
+      <c r="AG8">
+        <v>155.88</v>
+      </c>
+      <c r="AH8">
+        <v>0.8276220145379023</v>
+      </c>
+      <c r="AI8">
+        <v>0.813265306122449</v>
+      </c>
+      <c r="AJ8">
+        <v>0.8244129469007828</v>
+      </c>
+      <c r="AK8">
+        <v>0.809850374064838</v>
+      </c>
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <v>-0.154</v>
+      </c>
+      <c r="AQ8">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>Al Tawfeek Leasing Company (CASE:ATLC)</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D8">
+      <c r="D9">
         <v>0.0338</v>
       </c>
-      <c r="E8">
+      <c r="E9">
         <v>0.254</v>
       </c>
-      <c r="F8">
-        <v>0.15</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8">
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
         <v>8.66</v>
       </c>
-      <c r="L8">
+      <c r="L9">
         <v>0.2577380952380952</v>
       </c>
-      <c r="M8">
+      <c r="M9">
         <v>1.43</v>
       </c>
-      <c r="N8">
-        <v>0.03896457765667574</v>
-      </c>
-      <c r="O8">
+      <c r="N9">
+        <v>0.07044334975369458</v>
+      </c>
+      <c r="O9">
         <v>0.1651270207852194</v>
       </c>
-      <c r="P8">
+      <c r="P9">
         <v>1.43</v>
       </c>
-      <c r="Q8">
-        <v>0.03896457765667574</v>
-      </c>
-      <c r="R8">
+      <c r="Q9">
+        <v>0.07044334975369458</v>
+      </c>
+      <c r="R9">
         <v>0.1651270207852194</v>
       </c>
-      <c r="S8">
-        <v>0</v>
-      </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
-      <c r="U8">
-        <v>11.4</v>
-      </c>
-      <c r="V8">
-        <v>0.3106267029972752</v>
-      </c>
-      <c r="W8">
-        <v>0.3716738197424893</v>
-      </c>
-      <c r="X8">
-        <v>0.1138653195586078</v>
-      </c>
-      <c r="Y8">
-        <v>0.2578085001838814</v>
-      </c>
-      <c r="Z8">
-        <v>0.1464435146443515</v>
-      </c>
-      <c r="AA8">
-        <v>0</v>
-      </c>
-      <c r="AB8">
-        <v>0.0664355352648637</v>
-      </c>
-      <c r="AC8">
-        <v>-0.0664355352648637</v>
-      </c>
-      <c r="AD8">
-        <v>205.4</v>
-      </c>
-      <c r="AE8">
-        <v>0</v>
-      </c>
-      <c r="AF8">
-        <v>205.4</v>
-      </c>
-      <c r="AG8">
-        <v>194</v>
-      </c>
-      <c r="AH8">
-        <v>0.8484097480380007</v>
-      </c>
-      <c r="AI8">
-        <v>0.8725573491928632</v>
-      </c>
-      <c r="AJ8">
-        <v>0.8409189423493715</v>
-      </c>
-      <c r="AK8">
-        <v>0.8660714285714286</v>
-      </c>
-      <c r="AL8">
-        <v>0</v>
-      </c>
-      <c r="AM8">
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>9.84</v>
+      </c>
+      <c r="V9">
+        <v>0.4847290640394089</v>
+      </c>
+      <c r="W9">
+        <v>0.3172161172161172</v>
+      </c>
+      <c r="X9">
+        <v>0.1968169503809472</v>
+      </c>
+      <c r="Y9">
+        <v>0.12039916683517</v>
+      </c>
+      <c r="Z9">
+        <v>0.1800353640893747</v>
+      </c>
+      <c r="AA9">
+        <v>0</v>
+      </c>
+      <c r="AB9">
+        <v>0.1073905591197531</v>
+      </c>
+      <c r="AC9">
+        <v>-0.1073905591197531</v>
+      </c>
+      <c r="AD9">
+        <v>144</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <v>144</v>
+      </c>
+      <c r="AG9">
+        <v>134.16</v>
+      </c>
+      <c r="AH9">
+        <v>0.8764455264759585</v>
+      </c>
+      <c r="AI9">
+        <v>0.851063829787234</v>
+      </c>
+      <c r="AJ9">
+        <v>0.8685743881911173</v>
+      </c>
+      <c r="AK9">
+        <v>0.8418674698795181</v>
+      </c>
+      <c r="AL9">
+        <v>0</v>
+      </c>
+      <c r="AM9">
         <v>-0.417</v>
       </c>
-      <c r="AQ8">
+      <c r="AQ9">
         <v>-0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/egypt/egypt_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/egypt/egypt_financial_svcs_non_bank_insurance.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ9"/>
+  <dimension ref="A1:AQ11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,112 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.05010000000000001</v>
+        <v>0.0191</v>
       </c>
       <c r="E2">
-        <v>0.06958</v>
+        <v>0.1263</v>
+      </c>
+      <c r="F2">
+        <v>0.27</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>0.07804226234440814</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>0.07804226234440814</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>0.08766080771696613</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>0.05862816011007396</v>
       </c>
       <c r="K2">
-        <v>120.18</v>
+        <v>208.649</v>
       </c>
       <c r="L2">
-        <v>0.2957185039370079</v>
+        <v>0.3342935741305361</v>
       </c>
       <c r="M2">
-        <v>52.87</v>
+        <v>57.986</v>
       </c>
       <c r="N2">
-        <v>0.06285068949120304</v>
+        <v>0.02255299288242386</v>
       </c>
       <c r="O2">
-        <v>0.4399234481610916</v>
+        <v>0.277911708179766</v>
       </c>
       <c r="P2">
-        <v>52.87</v>
+        <v>54.083</v>
       </c>
       <c r="Q2">
-        <v>0.06285068949120304</v>
+        <v>0.02103496557893509</v>
       </c>
       <c r="R2">
-        <v>0.4399234481610916</v>
+        <v>0.2592056515967007</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>3.902999999999999</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.06730935053288722</v>
       </c>
       <c r="U2">
-        <v>433.67</v>
+        <v>599.4</v>
       </c>
       <c r="V2">
-        <v>0.5155373276271993</v>
+        <v>0.2331297888063475</v>
       </c>
       <c r="W2">
-        <v>0.1047305843663041</v>
+        <v>0.1394366197183099</v>
       </c>
       <c r="X2">
-        <v>0.08920636363396592</v>
+        <v>0.08220296431945237</v>
       </c>
       <c r="Y2">
-        <v>0.01552422073233815</v>
+        <v>0.0572336553988575</v>
       </c>
       <c r="Z2">
-        <v>0.1892891410259993</v>
+        <v>0.2691599158598443</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.08897998181366135</v>
+        <v>0.08615143781080839</v>
       </c>
       <c r="AC2">
-        <v>-0.08897998181366135</v>
+        <v>-0.09462439255855772</v>
       </c>
       <c r="AD2">
-        <v>1439.818</v>
+        <v>1255.55</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>0.4979726213165115</v>
       </c>
       <c r="AF2">
-        <v>1439.818</v>
+        <v>1256.047972621316</v>
       </c>
       <c r="AG2">
-        <v>1006.148</v>
+        <v>656.6479726213164</v>
       </c>
       <c r="AH2">
-        <v>0.6312172898241049</v>
+        <v>0.3281942536862549</v>
       </c>
       <c r="AI2">
-        <v>0.5526669937026384</v>
+        <v>0.4983233750219216</v>
       </c>
       <c r="AJ2">
-        <v>0.5446445390906315</v>
+        <v>0.2034384277183946</v>
       </c>
       <c r="AK2">
-        <v>0.4633321483107903</v>
+        <v>0.3417997894901094</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>1.553</v>
       </c>
       <c r="AM2">
-        <v>-0.571</v>
+        <v>-23.149</v>
+      </c>
+      <c r="AN2">
+        <v>20.3515795957402</v>
+      </c>
+      <c r="AO2">
+        <v>35.26722472633612</v>
+      </c>
+      <c r="AP2">
+        <v>10.64380031156398</v>
       </c>
       <c r="AQ2">
-        <v>-0</v>
+        <v>-2.365976932048901</v>
       </c>
     </row>
     <row r="3">
@@ -704,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Orascom Financial Holding S.A.E. (CASE:OFH)</t>
+          <t>Fawry for Banking Technology and Electronic Payments S.A.E. (CASE:FWRY)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -712,80 +724,116 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="G3">
+        <v>0.1633714880332987</v>
+      </c>
+      <c r="H3">
+        <v>0.1633714880332987</v>
+      </c>
+      <c r="I3">
+        <v>0.1810613943808533</v>
+      </c>
+      <c r="J3">
+        <v>0.1342019836756424</v>
+      </c>
       <c r="K3">
-        <v>0</v>
+        <v>19.5</v>
+      </c>
+      <c r="L3">
+        <v>0.2029136316337149</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>3.03</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.004992585269401878</v>
+      </c>
+      <c r="O3">
+        <v>0.1553846153846154</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>3.03</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.004992585269401878</v>
+      </c>
+      <c r="R3">
+        <v>0.1553846153846154</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
       <c r="U3">
-        <v>37.4</v>
+        <v>120</v>
       </c>
       <c r="V3">
-        <v>0.700374531835206</v>
+        <v>0.1977261492832427</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>0.1622296173044925</v>
       </c>
       <c r="X3">
-        <v>0.06316116379580984</v>
+        <v>0.07745872555696065</v>
       </c>
       <c r="Y3">
-        <v>-0.06316116379580984</v>
+        <v>0.08477089174753186</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>1.487155679356236</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>0.1995792422041045</v>
       </c>
       <c r="AB3">
-        <v>0.06323738105860478</v>
+        <v>0.07860716137805156</v>
       </c>
       <c r="AC3">
-        <v>-0.06323738105860478</v>
+        <v>0.1209720808260529</v>
       </c>
       <c r="AD3">
-        <v>0.118</v>
+        <v>28.9</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.118</v>
+        <v>28.9</v>
       </c>
       <c r="AG3">
-        <v>-37.282</v>
+        <v>-91.09999999999999</v>
       </c>
       <c r="AH3">
-        <v>0.002204865652677604</v>
+        <v>0.04545454545454546</v>
       </c>
       <c r="AI3">
-        <v>0.0008931409800330008</v>
+        <v>0.2196048632218845</v>
       </c>
       <c r="AJ3">
-        <v>-2.31306613723787</v>
+        <v>-0.1766188445133773</v>
       </c>
       <c r="AK3">
-        <v>-0.3936105069786102</v>
+        <v>-7.853448275862062</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>0.858</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>-11.642</v>
+      </c>
+      <c r="AN3">
+        <v>1.369668246445497</v>
+      </c>
+      <c r="AO3">
+        <v>20.27972027972028</v>
+      </c>
+      <c r="AP3">
+        <v>-4.317535545023696</v>
+      </c>
+      <c r="AQ3">
+        <v>-1.494588558666896</v>
       </c>
     </row>
     <row r="4">
@@ -796,7 +844,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Naeem Holding Company For Investments (S.A.E - Free Zone) (CASE:NAHO)</t>
+          <t>e-finance for Digital and Financial Investments S.A.E. (CASE:EFIH)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -804,107 +852,119 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D4">
-        <v>-0.134</v>
-      </c>
-      <c r="E4">
-        <v>-0.0924</v>
+      <c r="F4">
+        <v>0.27</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>0.3330365093499555</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>0.3330365093499555</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>0.3731077471059662</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>0.2654065417557904</v>
       </c>
       <c r="K4">
-        <v>2.83</v>
+        <v>41.1</v>
       </c>
       <c r="L4">
-        <v>0.3130530973451328</v>
+        <v>0.3659839715048976</v>
       </c>
       <c r="M4">
-        <v>-0</v>
+        <v>23.343</v>
       </c>
       <c r="N4">
-        <v>-0</v>
+        <v>0.0223271162123386</v>
       </c>
       <c r="O4">
-        <v>-0</v>
+        <v>0.5679562043795621</v>
       </c>
       <c r="P4">
-        <v>-0</v>
+        <v>23.1</v>
       </c>
       <c r="Q4">
-        <v>-0</v>
+        <v>0.02209469153515065</v>
       </c>
       <c r="R4">
-        <v>-0</v>
+        <v>0.5620437956204379</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>0.2429999999999986</v>
+      </c>
+      <c r="T4">
+        <v>0.01040997301118102</v>
       </c>
       <c r="U4">
-        <v>4.31</v>
+        <v>58.9</v>
       </c>
       <c r="V4">
-        <v>0.08086303939962476</v>
+        <v>0.05633668101386896</v>
       </c>
       <c r="W4">
-        <v>0.01382510991695164</v>
+        <v>0.1885321100917431</v>
       </c>
       <c r="X4">
-        <v>0.06835300221560923</v>
+        <v>0.07617732979335584</v>
       </c>
       <c r="Y4">
-        <v>-0.05452789229865759</v>
+        <v>0.1123547802983873</v>
       </c>
       <c r="Z4">
-        <v>0.05443159922928709</v>
+        <v>0.5905242677604249</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>0.1567290037291647</v>
       </c>
       <c r="AB4">
-        <v>0.07280026525643954</v>
+        <v>0.07626388614149526</v>
       </c>
       <c r="AC4">
-        <v>-0.07280026525643954</v>
+        <v>0.08046511758766947</v>
       </c>
       <c r="AD4">
-        <v>14.8</v>
+        <v>3.42</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>14.8</v>
+        <v>3.42</v>
       </c>
       <c r="AG4">
-        <v>10.49</v>
+        <v>-55.48</v>
       </c>
       <c r="AH4">
-        <v>0.2173274596182085</v>
+        <v>0.003260496510696716</v>
       </c>
       <c r="AI4">
-        <v>0.05875347360063517</v>
+        <v>0.02035471967622902</v>
       </c>
       <c r="AJ4">
-        <v>0.1644458379056279</v>
+        <v>-0.05603927193390032</v>
       </c>
       <c r="AK4">
-        <v>0.04236843168140879</v>
+        <v>-0.5084310850439883</v>
       </c>
       <c r="AL4">
-        <v>0</v>
+        <v>0.664</v>
       </c>
       <c r="AM4">
-        <v>0</v>
+        <v>-8.616</v>
+      </c>
+      <c r="AN4">
+        <v>0.076</v>
+      </c>
+      <c r="AO4">
+        <v>63.10240963855421</v>
+      </c>
+      <c r="AP4">
+        <v>-1.232888888888889</v>
+      </c>
+      <c r="AQ4">
+        <v>-4.863045496750233</v>
       </c>
     </row>
     <row r="5">
@@ -923,12 +983,6 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D5">
-        <v>0.22</v>
-      </c>
-      <c r="E5">
-        <v>0.136</v>
-      </c>
       <c r="G5">
         <v>0</v>
       </c>
@@ -936,94 +990,103 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>-0.0002874277514642067</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>-0.0001967703627600067</v>
       </c>
       <c r="K5">
-        <v>41.4</v>
+        <v>84.5</v>
       </c>
       <c r="L5">
-        <v>0.2758161225849434</v>
+        <v>0.4291518537328593</v>
       </c>
       <c r="M5">
-        <v>-0</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="N5">
-        <v>-0</v>
+        <v>0.01971549233162925</v>
       </c>
       <c r="O5">
-        <v>-0</v>
+        <v>0.1049704142011834</v>
       </c>
       <c r="P5">
-        <v>-0</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="Q5">
-        <v>-0</v>
+        <v>0.01971549233162925</v>
       </c>
       <c r="R5">
-        <v>-0</v>
+        <v>0.1049704142011834</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
       <c r="U5">
-        <v>291.6</v>
+        <v>307.7</v>
       </c>
       <c r="V5">
-        <v>1.146677152968934</v>
+        <v>0.683929762169371</v>
       </c>
       <c r="W5">
-        <v>0.1047305843663041</v>
+        <v>0.1784582893347413</v>
       </c>
       <c r="X5">
-        <v>0.07014568458973197</v>
+        <v>0.08001316389367039</v>
       </c>
       <c r="Y5">
-        <v>0.0345848997765721</v>
+        <v>0.0984451254410709</v>
       </c>
       <c r="Z5">
-        <v>0.3794236602628918</v>
+        <v>1.104331121129414</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>-0.0002172996353117997</v>
       </c>
       <c r="AB5">
-        <v>0.0752158246877923</v>
+        <v>0.0827325570309214</v>
       </c>
       <c r="AC5">
-        <v>-0.0752158246877923</v>
+        <v>-0.0829498566662332</v>
       </c>
       <c r="AD5">
-        <v>94.8</v>
+        <v>60.7</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>0.4979726213165115</v>
       </c>
       <c r="AF5">
-        <v>94.8</v>
+        <v>61.19797262131652</v>
       </c>
       <c r="AG5">
-        <v>-196.8</v>
+        <v>-246.5020273786835</v>
       </c>
       <c r="AH5">
-        <v>0.2715554282440561</v>
+        <v>0.1197382417845344</v>
       </c>
       <c r="AI5">
-        <v>0.2</v>
+        <v>0.1328952053207881</v>
       </c>
       <c r="AJ5">
-        <v>-3.422608695652174</v>
+        <v>-1.211919785639248</v>
       </c>
       <c r="AK5">
-        <v>-1.078947368421053</v>
+        <v>-1.613254568433289</v>
       </c>
       <c r="AL5">
         <v>0</v>
       </c>
       <c r="AM5">
         <v>0</v>
+      </c>
+      <c r="AN5">
+        <v>1411.627906976744</v>
+      </c>
+      <c r="AP5">
+        <v>-5732.60528787636</v>
       </c>
     </row>
     <row r="6">
@@ -1034,7 +1097,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Contact Financial Holding S.A.E. (CASE:CNFN)</t>
+          <t>Naeem Holding Company For Investments (S.A.E - Free Zone) (CASE:NAHO)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1042,6 +1105,9 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D6">
+        <v>-0.0461</v>
+      </c>
       <c r="G6">
         <v>0</v>
       </c>
@@ -1055,85 +1121,82 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>24.1</v>
+        <v>0.289</v>
       </c>
       <c r="L6">
-        <v>0.2104803493449782</v>
+        <v>0.02892892892892893</v>
       </c>
       <c r="M6">
-        <v>17.8</v>
+        <v>-0</v>
       </c>
       <c r="N6">
-        <v>0.09314495028780743</v>
+        <v>-0</v>
       </c>
       <c r="O6">
-        <v>0.7385892116182573</v>
+        <v>-0</v>
       </c>
       <c r="P6">
-        <v>17.8</v>
+        <v>-0</v>
       </c>
       <c r="Q6">
-        <v>0.09314495028780743</v>
+        <v>-0</v>
       </c>
       <c r="R6">
-        <v>0.7385892116182573</v>
+        <v>-0</v>
       </c>
       <c r="S6">
         <v>0</v>
       </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
       <c r="U6">
-        <v>26.8</v>
+        <v>2.71</v>
       </c>
       <c r="V6">
-        <v>0.1402407116692831</v>
+        <v>0.05519348268839103</v>
       </c>
       <c r="W6">
-        <v>0.1579292267365662</v>
+        <v>0.001427865612648221</v>
       </c>
       <c r="X6">
-        <v>0.08920636363396592</v>
+        <v>0.08220296431945237</v>
       </c>
       <c r="Y6">
-        <v>0.06872286310260028</v>
+        <v>-0.08077509870680415</v>
       </c>
       <c r="Z6">
-        <v>0.3853661820140011</v>
+        <v>0.06323185011709602</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.08897998181366135</v>
+        <v>0.08615143781080839</v>
       </c>
       <c r="AC6">
-        <v>-0.08897998181366135</v>
+        <v>-0.08615143781080839</v>
       </c>
       <c r="AD6">
-        <v>264.5</v>
+        <v>10.4</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>264.5</v>
+        <v>10.4</v>
       </c>
       <c r="AG6">
-        <v>237.7</v>
+        <v>7.69</v>
       </c>
       <c r="AH6">
-        <v>0.5805531167690957</v>
+        <v>0.1747899159663866</v>
       </c>
       <c r="AI6">
-        <v>0.6444931773879142</v>
+        <v>0.04718693284936479</v>
       </c>
       <c r="AJ6">
-        <v>0.5543376865671642</v>
+        <v>0.1354111639373129</v>
       </c>
       <c r="AK6">
-        <v>0.6196558915537017</v>
+        <v>0.03532546281409344</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1150,7 +1213,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CI Capital Holding For Financial Investments (S.A.E) (CASE:CICH)</t>
+          <t>Orascom Financial Holding S.A.E. (CASE:OFH)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1159,103 +1222,115 @@
         </is>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>-8.977505112474438</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>-8.977505112474438</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>-9.263803680981596</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>-4.631901840490798</v>
       </c>
       <c r="K7">
-        <v>38.6</v>
+        <v>1.48</v>
       </c>
       <c r="L7">
-        <v>0.4200217627856366</v>
+        <v>3.026584867075665</v>
       </c>
       <c r="M7">
-        <v>29</v>
+        <v>3.66</v>
       </c>
       <c r="N7">
-        <v>0.1230899830220713</v>
+        <v>0.07305389221556886</v>
       </c>
       <c r="O7">
-        <v>0.7512953367875648</v>
+        <v>2.472972972972973</v>
       </c>
       <c r="P7">
-        <v>29</v>
+        <v>-0</v>
       </c>
       <c r="Q7">
-        <v>0.1230899830220713</v>
+        <v>-0</v>
       </c>
       <c r="R7">
-        <v>0.7512953367875648</v>
+        <v>-0</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U7">
-        <v>60.2</v>
+        <v>20</v>
       </c>
       <c r="V7">
-        <v>0.2555178268251274</v>
+        <v>0.3992015968063872</v>
       </c>
       <c r="W7">
-        <v>0.185309649543927</v>
+        <v>0.01084249084249084</v>
       </c>
       <c r="X7">
-        <v>0.1240943006981008</v>
+        <v>0.07627313319057716</v>
       </c>
       <c r="Y7">
-        <v>0.0612153488458262</v>
+        <v>-0.06543064234808632</v>
       </c>
       <c r="Z7">
-        <v>0.1224190755295058</v>
+        <v>0.003924558587479935</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>-0.01817817014446228</v>
       </c>
       <c r="AB7">
-        <v>0.1017046728872097</v>
+        <v>0.07644622241409543</v>
       </c>
       <c r="AC7">
-        <v>-0.1017046728872097</v>
+        <v>-0.09462439255855772</v>
       </c>
       <c r="AD7">
-        <v>762.2</v>
+        <v>0.33</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>762.2</v>
+        <v>0.33</v>
       </c>
       <c r="AG7">
-        <v>702</v>
+        <v>-19.67</v>
       </c>
       <c r="AH7">
-        <v>0.7638805371817999</v>
+        <v>0.006543723973825104</v>
       </c>
       <c r="AI7">
-        <v>0.7844792095512557</v>
+        <v>0.00398406374501992</v>
       </c>
       <c r="AJ7">
-        <v>0.7487201365187713</v>
+        <v>-0.6464015773907329</v>
       </c>
       <c r="AK7">
-        <v>0.7702435813034891</v>
+        <v>-0.3130670062072259</v>
       </c>
       <c r="AL7">
-        <v>0</v>
+        <v>0.031</v>
       </c>
       <c r="AM7">
-        <v>0</v>
+        <v>-2.419</v>
+      </c>
+      <c r="AN7">
+        <v>-0.07415730337078652</v>
+      </c>
+      <c r="AO7">
+        <v>-146.1290322580645</v>
+      </c>
+      <c r="AP7">
+        <v>4.420224719101124</v>
+      </c>
+      <c r="AQ7">
+        <v>1.872674658949979</v>
       </c>
     </row>
     <row r="8">
@@ -1266,7 +1341,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>International Company for Leasing S.A.E. (CASE:ICLE)</t>
+          <t>Contact Financial Holding S.A.E. (CASE:CNFN)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1275,10 +1350,10 @@
         </is>
       </c>
       <c r="D8">
-        <v>-0.255</v>
+        <v>0.0191</v>
       </c>
       <c r="E8">
-        <v>0.00316</v>
+        <v>0.167</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1293,28 +1368,28 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>4.59</v>
+        <v>19.8</v>
       </c>
       <c r="L8">
-        <v>0.6322314049586777</v>
+        <v>0.1935483870967742</v>
       </c>
       <c r="M8">
-        <v>4.64</v>
+        <v>12.6</v>
       </c>
       <c r="N8">
-        <v>0.1397590361445783</v>
+        <v>0.08588957055214724</v>
       </c>
       <c r="O8">
-        <v>1.010893246187364</v>
+        <v>0.6363636363636364</v>
       </c>
       <c r="P8">
-        <v>4.64</v>
+        <v>12.6</v>
       </c>
       <c r="Q8">
-        <v>0.1397590361445783</v>
+        <v>0.08588957055214724</v>
       </c>
       <c r="R8">
-        <v>1.010893246187364</v>
+        <v>0.6363636363636364</v>
       </c>
       <c r="S8">
         <v>0</v>
@@ -1323,64 +1398,61 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>3.52</v>
+        <v>24</v>
       </c>
       <c r="V8">
-        <v>0.1060240963855422</v>
+        <v>0.16359918200409</v>
       </c>
       <c r="W8">
-        <v>0.1045558086560364</v>
+        <v>0.1394366197183099</v>
       </c>
       <c r="X8">
-        <v>0.153610821079894</v>
+        <v>0.1235504145490126</v>
       </c>
       <c r="Y8">
-        <v>-0.0490550124238576</v>
+        <v>0.01588620516929731</v>
       </c>
       <c r="Z8">
-        <v>0.03650993210963037</v>
+        <v>0.27059912709959</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.1073617312023741</v>
+        <v>0.1078046662290214</v>
       </c>
       <c r="AC8">
-        <v>-0.1073617312023741</v>
+        <v>-0.1078046662290214</v>
       </c>
       <c r="AD8">
-        <v>159.4</v>
+        <v>241</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>159.4</v>
+        <v>241</v>
       </c>
       <c r="AG8">
-        <v>155.88</v>
+        <v>217</v>
       </c>
       <c r="AH8">
-        <v>0.8276220145379023</v>
+        <v>0.6216146505029663</v>
       </c>
       <c r="AI8">
-        <v>0.813265306122449</v>
+        <v>0.711754282339043</v>
       </c>
       <c r="AJ8">
-        <v>0.8244129469007828</v>
+        <v>0.5966455870222711</v>
       </c>
       <c r="AK8">
-        <v>0.809850374064838</v>
+        <v>0.6897647806738715</v>
       </c>
       <c r="AL8">
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>-0.154</v>
-      </c>
-      <c r="AQ8">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1391,120 +1463,367 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>CI Capital Holding For Financial Investments (S.A.E) (CASE:CICH)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D9">
+        <v>0.139</v>
+      </c>
+      <c r="E9">
+        <v>0.226</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>34.2</v>
+      </c>
+      <c r="L9">
+        <v>0.4535809018567639</v>
+      </c>
+      <c r="M9">
+        <v>0.283</v>
+      </c>
+      <c r="N9">
+        <v>0.00168955223880597</v>
+      </c>
+      <c r="O9">
+        <v>0.008274853801169589</v>
+      </c>
+      <c r="P9">
+        <v>0.283</v>
+      </c>
+      <c r="Q9">
+        <v>0.00168955223880597</v>
+      </c>
+      <c r="R9">
+        <v>0.008274853801169589</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>54.9</v>
+      </c>
+      <c r="V9">
+        <v>0.3277611940298507</v>
+      </c>
+      <c r="W9">
+        <v>0.1834763948497854</v>
+      </c>
+      <c r="X9">
+        <v>0.1822236399580389</v>
+      </c>
+      <c r="Y9">
+        <v>0.001252754891746533</v>
+      </c>
+      <c r="Z9">
+        <v>0.0867863720073665</v>
+      </c>
+      <c r="AA9">
+        <v>0</v>
+      </c>
+      <c r="AB9">
+        <v>0.1197352195502663</v>
+      </c>
+      <c r="AC9">
+        <v>-0.1197352195502663</v>
+      </c>
+      <c r="AD9">
+        <v>615.3</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <v>615.3</v>
+      </c>
+      <c r="AG9">
+        <v>560.4</v>
+      </c>
+      <c r="AH9">
+        <v>0.7860245273377618</v>
+      </c>
+      <c r="AI9">
+        <v>0.7911791179117912</v>
+      </c>
+      <c r="AJ9">
+        <v>0.7698859733479874</v>
+      </c>
+      <c r="AK9">
+        <v>0.7753182069728832</v>
+      </c>
+      <c r="AL9">
+        <v>0</v>
+      </c>
+      <c r="AM9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
           <t>Al Tawfeek Leasing Company (CASE:ATLC)</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D9">
-        <v>0.0338</v>
-      </c>
-      <c r="E9">
-        <v>0.254</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9">
-        <v>0</v>
-      </c>
-      <c r="K9">
-        <v>8.66</v>
-      </c>
-      <c r="L9">
-        <v>0.2577380952380952</v>
-      </c>
-      <c r="M9">
-        <v>1.43</v>
-      </c>
-      <c r="N9">
-        <v>0.07044334975369458</v>
-      </c>
-      <c r="O9">
-        <v>0.1651270207852194</v>
-      </c>
-      <c r="P9">
-        <v>1.43</v>
-      </c>
-      <c r="Q9">
-        <v>0.07044334975369458</v>
-      </c>
-      <c r="R9">
-        <v>0.1651270207852194</v>
-      </c>
-      <c r="S9">
-        <v>0</v>
-      </c>
-      <c r="T9">
-        <v>0</v>
-      </c>
-      <c r="U9">
-        <v>9.84</v>
-      </c>
-      <c r="V9">
-        <v>0.4847290640394089</v>
-      </c>
-      <c r="W9">
-        <v>0.3172161172161172</v>
-      </c>
-      <c r="X9">
-        <v>0.1968169503809472</v>
-      </c>
-      <c r="Y9">
-        <v>0.12039916683517</v>
-      </c>
-      <c r="Z9">
-        <v>0.1800353640893747</v>
-      </c>
-      <c r="AA9">
-        <v>0</v>
-      </c>
-      <c r="AB9">
-        <v>0.1073905591197531</v>
-      </c>
-      <c r="AC9">
-        <v>-0.1073905591197531</v>
-      </c>
-      <c r="AD9">
-        <v>144</v>
-      </c>
-      <c r="AE9">
-        <v>0</v>
-      </c>
-      <c r="AF9">
-        <v>144</v>
-      </c>
-      <c r="AG9">
-        <v>134.16</v>
-      </c>
-      <c r="AH9">
-        <v>0.8764455264759585</v>
-      </c>
-      <c r="AI9">
-        <v>0.851063829787234</v>
-      </c>
-      <c r="AJ9">
-        <v>0.8685743881911173</v>
-      </c>
-      <c r="AK9">
-        <v>0.8418674698795181</v>
-      </c>
-      <c r="AL9">
-        <v>0</v>
-      </c>
-      <c r="AM9">
-        <v>-0.417</v>
-      </c>
-      <c r="AQ9">
+      <c r="D10">
+        <v>0.04940000000000001</v>
+      </c>
+      <c r="E10">
+        <v>0.08560000000000001</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>3.1</v>
+      </c>
+      <c r="L10">
+        <v>0.1270491803278689</v>
+      </c>
+      <c r="M10">
+        <v>3.59</v>
+      </c>
+      <c r="N10">
+        <v>0.1250871080139373</v>
+      </c>
+      <c r="O10">
+        <v>1.158064516129032</v>
+      </c>
+      <c r="P10">
+        <v>3.59</v>
+      </c>
+      <c r="Q10">
+        <v>0.1250871080139373</v>
+      </c>
+      <c r="R10">
+        <v>1.158064516129032</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>7.78</v>
+      </c>
+      <c r="V10">
+        <v>0.2710801393728223</v>
+      </c>
+      <c r="W10">
+        <v>0.123015873015873</v>
+      </c>
+      <c r="X10">
+        <v>0.2383734650045935</v>
+      </c>
+      <c r="Y10">
+        <v>-0.1153575919887204</v>
+      </c>
+      <c r="Z10">
+        <v>0.1531124497991968</v>
+      </c>
+      <c r="AA10">
+        <v>0</v>
+      </c>
+      <c r="AB10">
+        <v>0.1232252648832578</v>
+      </c>
+      <c r="AC10">
+        <v>-0.1232252648832578</v>
+      </c>
+      <c r="AD10">
+        <v>161.2</v>
+      </c>
+      <c r="AE10">
+        <v>0</v>
+      </c>
+      <c r="AF10">
+        <v>161.2</v>
+      </c>
+      <c r="AG10">
+        <v>153.42</v>
+      </c>
+      <c r="AH10">
+        <v>0.8488678251711428</v>
+      </c>
+      <c r="AI10">
+        <v>0.8960533629794331</v>
+      </c>
+      <c r="AJ10">
+        <v>0.842411596749396</v>
+      </c>
+      <c r="AK10">
+        <v>0.8913548686962585</v>
+      </c>
+      <c r="AL10">
+        <v>0</v>
+      </c>
+      <c r="AM10">
+        <v>-0.351</v>
+      </c>
+      <c r="AQ10">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>International Company for Leasing S.A.E. (CASE:ICLE)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D11">
+        <v>-0.209</v>
+      </c>
+      <c r="E11">
+        <v>0.05599999999999999</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>4.68</v>
+      </c>
+      <c r="L11">
+        <v>0.7464114832535885</v>
+      </c>
+      <c r="M11">
+        <v>2.61</v>
+      </c>
+      <c r="N11">
+        <v>0.09775280898876404</v>
+      </c>
+      <c r="O11">
+        <v>0.5576923076923077</v>
+      </c>
+      <c r="P11">
+        <v>2.61</v>
+      </c>
+      <c r="Q11">
+        <v>0.09775280898876404</v>
+      </c>
+      <c r="R11">
+        <v>0.5576923076923077</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <v>3.41</v>
+      </c>
+      <c r="V11">
+        <v>0.1277153558052435</v>
+      </c>
+      <c r="W11">
+        <v>0.1264864864864865</v>
+      </c>
+      <c r="X11">
+        <v>0.2214194529138531</v>
+      </c>
+      <c r="Y11">
+        <v>-0.09493296642736665</v>
+      </c>
+      <c r="Z11">
+        <v>0.03182902685415503</v>
+      </c>
+      <c r="AA11">
+        <v>0</v>
+      </c>
+      <c r="AB11">
+        <v>0.1241339807738811</v>
+      </c>
+      <c r="AC11">
+        <v>-0.1241339807738811</v>
+      </c>
+      <c r="AD11">
+        <v>134.3</v>
+      </c>
+      <c r="AE11">
+        <v>0</v>
+      </c>
+      <c r="AF11">
+        <v>134.3</v>
+      </c>
+      <c r="AG11">
+        <v>130.89</v>
+      </c>
+      <c r="AH11">
+        <v>0.8341614906832299</v>
+      </c>
+      <c r="AI11">
+        <v>0.8341614906832299</v>
+      </c>
+      <c r="AJ11">
+        <v>0.8305730059013897</v>
+      </c>
+      <c r="AK11">
+        <v>0.8305730059013897</v>
+      </c>
+      <c r="AL11">
+        <v>0</v>
+      </c>
+      <c r="AM11">
+        <v>-0.121</v>
+      </c>
+      <c r="AQ11">
         <v>-0</v>
       </c>
     </row>
